--- a/output/roomself_excel/5692.xlsx
+++ b/output/roomself_excel/5692.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>86000</v>
+        <v>602</v>
       </c>
       <c r="D2" t="n">
-        <v>2380</v>
+        <v>1212</v>
       </c>
       <c r="E2" t="n">
-        <v>334</v>
+        <v>27</v>
       </c>
       <c r="F2" t="n">
-        <v>321</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16050</v>
+        <v>77796</v>
       </c>
       <c r="D3" t="n">
-        <v>1028</v>
+        <v>2268</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>266</v>
       </c>
       <c r="F3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>165802</v>
+        <v>202445</v>
       </c>
       <c r="D4" t="n">
-        <v>5740</v>
+        <v>4392</v>
       </c>
       <c r="E4" t="n">
-        <v>927</v>
+        <v>657</v>
       </c>
       <c r="F4" t="n">
-        <v>668</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45738</v>
+        <v>74804</v>
       </c>
       <c r="D5" t="n">
-        <v>1724</v>
+        <v>2484</v>
       </c>
       <c r="E5" t="n">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="F5" t="n">
-        <v>188</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90228</v>
+        <v>49170</v>
       </c>
       <c r="D6" t="n">
-        <v>2404</v>
+        <v>1852</v>
       </c>
       <c r="E6" t="n">
-        <v>344</v>
+        <v>165</v>
       </c>
       <c r="F6" t="n">
-        <v>292</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>106400</v>
+        <v>86000</v>
       </c>
       <c r="D7" t="n">
-        <v>2640</v>
+        <v>2380</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20384</v>
+        <v>90228</v>
       </c>
       <c r="D8" t="n">
-        <v>1176</v>
+        <v>2404</v>
       </c>
       <c r="E8" t="n">
-        <v>208</v>
+        <v>344</v>
       </c>
       <c r="F8" t="n">
-        <v>139</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12320</v>
+        <v>96772</v>
       </c>
       <c r="D9" t="n">
-        <v>888</v>
+        <v>2524</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>334</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17100</v>
+        <v>91809</v>
       </c>
       <c r="D10" t="n">
-        <v>1056</v>
+        <v>2424</v>
       </c>
       <c r="E10" t="n">
-        <v>454</v>
+        <v>330</v>
       </c>
       <c r="F10" t="n">
-        <v>150</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>390881</v>
+        <v>16050</v>
       </c>
       <c r="D11" t="n">
-        <v>9520</v>
+        <v>1028</v>
       </c>
       <c r="E11" t="n">
-        <v>1110</v>
+        <v>107</v>
       </c>
       <c r="F11" t="n">
-        <v>657</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50298</v>
+        <v>17100</v>
       </c>
       <c r="D12" t="n">
-        <v>1876</v>
+        <v>1056</v>
       </c>
       <c r="E12" t="n">
-        <v>316</v>
+        <v>114</v>
       </c>
       <c r="F12" t="n">
-        <v>219</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10584</v>
+        <v>40112</v>
       </c>
       <c r="D13" t="n">
-        <v>980</v>
+        <v>1608</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>96772</v>
+        <v>44955</v>
       </c>
       <c r="D14" t="n">
-        <v>2524</v>
+        <v>1712</v>
       </c>
       <c r="E14" t="n">
-        <v>334</v>
+        <v>185</v>
       </c>
       <c r="F14" t="n">
-        <v>333</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
@@ -752,17 +752,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>49170</v>
+        <v>90998</v>
       </c>
       <c r="D15" t="n">
-        <v>1852</v>
+        <v>3668</v>
       </c>
       <c r="E15" t="n">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="F15" t="n">
         <v>25</v>
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>91809</v>
+        <v>110038</v>
       </c>
       <c r="D16" t="n">
-        <v>2424</v>
+        <v>4748</v>
       </c>
       <c r="E16" t="n">
-        <v>330</v>
+        <v>657</v>
       </c>
       <c r="F16" t="n">
-        <v>329</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23736</v>
+        <v>20384</v>
       </c>
       <c r="D17" t="n">
-        <v>1252</v>
+        <v>1176</v>
       </c>
       <c r="E17" t="n">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>40112</v>
+        <v>32686</v>
       </c>
       <c r="D18" t="n">
-        <v>1608</v>
+        <v>1580</v>
       </c>
       <c r="E18" t="n">
-        <v>218</v>
+        <v>302</v>
       </c>
       <c r="F18" t="n">
-        <v>25</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20096</v>
+        <v>121160</v>
       </c>
       <c r="D19" t="n">
-        <v>1140</v>
+        <v>2840</v>
       </c>
       <c r="E19" t="n">
-        <v>128</v>
+        <v>474</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32686</v>
+        <v>217105</v>
       </c>
       <c r="D20" t="n">
-        <v>1580</v>
+        <v>3748</v>
       </c>
       <c r="E20" t="n">
-        <v>302</v>
+        <v>539</v>
       </c>
       <c r="F20" t="n">
-        <v>143</v>
+        <v>473</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>16048</v>
+        <v>45738</v>
       </c>
       <c r="D21" t="n">
-        <v>1016</v>
+        <v>1724</v>
       </c>
       <c r="E21" t="n">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="F21" t="n">
-        <v>143</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22">
@@ -906,20 +906,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>121160</v>
+        <v>106400</v>
       </c>
       <c r="D22" t="n">
-        <v>2840</v>
+        <v>2640</v>
       </c>
       <c r="E22" t="n">
-        <v>474</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>445</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>215680</v>
+        <v>12320</v>
       </c>
       <c r="D23" t="n">
-        <v>3780</v>
+        <v>888</v>
       </c>
       <c r="E23" t="n">
-        <v>566</v>
+        <v>110</v>
       </c>
       <c r="F23" t="n">
-        <v>511</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -950,20 +950,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>217105</v>
+        <v>50298</v>
       </c>
       <c r="D24" t="n">
-        <v>3748</v>
+        <v>1876</v>
       </c>
       <c r="E24" t="n">
-        <v>539</v>
+        <v>316</v>
       </c>
       <c r="F24" t="n">
-        <v>473</v>
+        <v>219</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>124233</v>
+        <v>10584</v>
       </c>
       <c r="D25" t="n">
-        <v>3048</v>
+        <v>980</v>
       </c>
       <c r="E25" t="n">
-        <v>684</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -994,20 +994,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>44955</v>
+        <v>23736</v>
       </c>
       <c r="D26" t="n">
-        <v>1712</v>
+        <v>1252</v>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="F26" t="n">
-        <v>125</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1020,15 +1020,103 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>20096</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E27" t="n">
+        <v>128</v>
+      </c>
+      <c r="F27" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>16048</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E28" t="n">
+        <v>161</v>
+      </c>
+      <c r="F28" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>215680</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3780</v>
+      </c>
+      <c r="E29" t="n">
+        <v>566</v>
+      </c>
+      <c r="F29" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>124233</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3048</v>
+      </c>
+      <c r="E30" t="n">
+        <v>397</v>
+      </c>
+      <c r="F30" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>33534</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D31" t="n">
         <v>1524</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E31" t="n">
         <v>138</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F31" t="n">
         <v>29</v>
       </c>
     </row>

--- a/output/roomself_excel/5692.xlsx
+++ b/output/roomself_excel/5692.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,62 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
         </is>
       </c>
     </row>
@@ -475,12 +525,18 @@
       <c r="D2" t="n">
         <v>1212</v>
       </c>
-      <c r="E2" t="n">
-        <v>27</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +553,26 @@
       <c r="D3" t="n">
         <v>2268</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>266</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>27</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +589,34 @@
       <c r="D4" t="n">
         <v>4392</v>
       </c>
-      <c r="E4" t="n">
-        <v>657</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>455</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>592</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +633,26 @@
       <c r="D5" t="n">
         <v>2484</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>213</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>25</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +669,34 @@
       <c r="D6" t="n">
         <v>1852</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>298</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>165</v>
       </c>
-      <c r="F6" t="n">
+      <c r="J6" t="n">
         <v>25</v>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +713,34 @@
       <c r="D7" t="n">
         <v>2380</v>
       </c>
-      <c r="E7" t="n">
-        <v>334</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>321</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>285</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +757,42 @@
       <c r="D8" t="n">
         <v>2404</v>
       </c>
-      <c r="E8" t="n">
-        <v>344</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>292</v>
       </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>309</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>11</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +809,34 @@
       <c r="D9" t="n">
         <v>2524</v>
       </c>
-      <c r="E9" t="n">
-        <v>334</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>333</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>309</v>
+      </c>
+      <c r="J9" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +853,34 @@
       <c r="D10" t="n">
         <v>2424</v>
       </c>
-      <c r="E10" t="n">
-        <v>330</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>329</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="G10" t="n">
+        <v>26</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>303</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +897,26 @@
       <c r="D11" t="n">
         <v>1028</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>107</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>25</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +933,26 @@
       <c r="D12" t="n">
         <v>1056</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>114</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>27</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +969,26 @@
       <c r="D13" t="n">
         <v>1608</v>
       </c>
-      <c r="E13" t="n">
-        <v>218</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F13" t="n">
+        <v>207</v>
+      </c>
+      <c r="G13" t="n">
         <v>25</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1005,26 @@
       <c r="D14" t="n">
         <v>1712</v>
       </c>
-      <c r="E14" t="n">
-        <v>185</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>125</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="G14" t="n">
+        <v>29</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1041,26 @@
       <c r="D15" t="n">
         <v>3668</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>137</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>25</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1077,26 @@
       <c r="D16" t="n">
         <v>4748</v>
       </c>
-      <c r="E16" t="n">
-        <v>657</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>179</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1113,34 @@
       <c r="D17" t="n">
         <v>1176</v>
       </c>
-      <c r="E17" t="n">
-        <v>208</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>139</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="G17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>112</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1157,34 @@
       <c r="D18" t="n">
         <v>1580</v>
       </c>
-      <c r="E18" t="n">
-        <v>302</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>143</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>118</v>
+      </c>
+      <c r="J18" t="n">
+        <v>25</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1201,34 @@
       <c r="D19" t="n">
         <v>2840</v>
       </c>
-      <c r="E19" t="n">
-        <v>474</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>286</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>91</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1245,42 @@
       <c r="D20" t="n">
         <v>3748</v>
       </c>
-      <c r="E20" t="n">
-        <v>539</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>473</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="G20" t="n">
+        <v>25</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>383</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>422</v>
+      </c>
+      <c r="M20" t="n">
+        <v>25</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1297,34 @@
       <c r="D21" t="n">
         <v>1724</v>
       </c>
-      <c r="E21" t="n">
-        <v>199</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F21" t="n">
-        <v>188</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1341,18 @@
       <c r="D22" t="n">
         <v>2640</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,12 +1369,26 @@
       <c r="D23" t="n">
         <v>888</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>110</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>27</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,12 +1405,26 @@
       <c r="D24" t="n">
         <v>1876</v>
       </c>
-      <c r="E24" t="n">
-        <v>316</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>219</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="G24" t="n">
+        <v>26</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1441,18 @@
       <c r="D25" t="n">
         <v>980</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1469,26 @@
       <c r="D26" t="n">
         <v>1252</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>129</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>25</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1505,26 @@
       <c r="D27" t="n">
         <v>1140</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>128</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>27</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1541,34 @@
       <c r="D28" t="n">
         <v>1016</v>
       </c>
-      <c r="E28" t="n">
-        <v>161</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>143</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="G28" t="n">
+        <v>25</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>118</v>
+      </c>
+      <c r="J28" t="n">
+        <v>25</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1585,42 @@
       <c r="D29" t="n">
         <v>3780</v>
       </c>
-      <c r="E29" t="n">
-        <v>566</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>511</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="G29" t="n">
+        <v>36</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>938</v>
+      </c>
+      <c r="J29" t="n">
+        <v>33</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>63</v>
+      </c>
+      <c r="M29" t="n">
+        <v>30</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,11 +1637,49 @@
       <c r="D30" t="n">
         <v>3048</v>
       </c>
-      <c r="E30" t="n">
-        <v>397</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>302</v>
+        <v>42</v>
+      </c>
+      <c r="G30" t="n">
+        <v>33</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>239</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>306</v>
+      </c>
+      <c r="M30" t="n">
+        <v>30</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>365</v>
+      </c>
+      <c r="P30" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -1113,12 +1697,34 @@
       <c r="D31" t="n">
         <v>1524</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>138</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>29</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>243</v>
+      </c>
+      <c r="J31" t="n">
+        <v>28</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
